--- a/data/indonesia_model_inputs_public_health.xlsx
+++ b/data/indonesia_model_inputs_public_health.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://uwnetid-my.sharepoint.com/personal/wrgg_uw_edu/Documents/02Work/WorldBank-Indonesia/uw-wb-indonesia-ncd/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="55" documentId="11_4329EEFB852386115C62C6D576342767CA1B238E" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{96546651-13E9-4DA1-8E9F-00B8441306FE}"/>
+  <xr:revisionPtr revIDLastSave="58" documentId="11_4329EEFB852386115C62C6D576342767CA1B238E" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3135964A-B0BD-4C55-A8F1-78CE430B8713}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3550,43 +3550,6 @@
     <xf numFmtId="164" fontId="18" fillId="7" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -3607,6 +3570,43 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -4482,6 +4482,168 @@
     </xdr:sp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>609600</xdr:colOff>
+      <xdr:row>33</xdr:row>
+      <xdr:rowOff>7620</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="3" name="AutoShape 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{67D80823-D3AC-F508-D18A-38B7E63EC3E1}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="7620000" cy="6797040"/>
+        </a:xfrm>
+        <a:custGeom>
+          <a:avLst/>
+          <a:gdLst/>
+          <a:ahLst/>
+          <a:cxnLst/>
+          <a:rect l="0" t="0" r="0" b="0"/>
+          <a:pathLst/>
+        </a:custGeom>
+        <a:solidFill>
+          <a:srgbClr val="FFFFFF"/>
+        </a:solidFill>
+        <a:ln w="9525">
+          <a:solidFill>
+            <a:srgbClr val="000000"/>
+          </a:solidFill>
+          <a:round/>
+          <a:headEnd/>
+          <a:tailEnd/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>609600</xdr:colOff>
+      <xdr:row>33</xdr:row>
+      <xdr:rowOff>7620</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="4" name="AutoShape 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B8BBD5A2-4FD9-8F9A-DD76-6D7D6A49A1DF}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="7620000" cy="6797040"/>
+        </a:xfrm>
+        <a:custGeom>
+          <a:avLst/>
+          <a:gdLst/>
+          <a:ahLst/>
+          <a:cxnLst/>
+          <a:rect l="0" t="0" r="0" b="0"/>
+          <a:pathLst/>
+        </a:custGeom>
+        <a:solidFill>
+          <a:srgbClr val="FFFFFF"/>
+        </a:solidFill>
+        <a:ln w="9525">
+          <a:solidFill>
+            <a:srgbClr val="000000"/>
+          </a:solidFill>
+          <a:round/>
+          <a:headEnd/>
+          <a:tailEnd/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>609600</xdr:colOff>
+      <xdr:row>33</xdr:row>
+      <xdr:rowOff>7620</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="5" name="AutoShape 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8E45FBA2-253C-D85B-AF5A-9FCED20FE4D7}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="7620000" cy="6797040"/>
+        </a:xfrm>
+        <a:custGeom>
+          <a:avLst/>
+          <a:gdLst/>
+          <a:ahLst/>
+          <a:cxnLst/>
+          <a:rect l="0" t="0" r="0" b="0"/>
+          <a:pathLst/>
+        </a:custGeom>
+        <a:solidFill>
+          <a:srgbClr val="FFFFFF"/>
+        </a:solidFill>
+        <a:ln w="9525">
+          <a:solidFill>
+            <a:srgbClr val="000000"/>
+          </a:solidFill>
+          <a:round/>
+          <a:headEnd/>
+          <a:tailEnd/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
 </xdr:wsDr>
 </file>
 
@@ -4555,6 +4717,168 @@
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
               <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0D939F5A-B870-90B0-0DC1-336D044B2EE6}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="7620000" cy="7620000"/>
+        </a:xfrm>
+        <a:custGeom>
+          <a:avLst/>
+          <a:gdLst/>
+          <a:ahLst/>
+          <a:cxnLst/>
+          <a:rect l="0" t="0" r="0" b="0"/>
+          <a:pathLst/>
+        </a:custGeom>
+        <a:solidFill>
+          <a:srgbClr val="FFFFFF"/>
+        </a:solidFill>
+        <a:ln w="9525">
+          <a:solidFill>
+            <a:srgbClr val="000000"/>
+          </a:solidFill>
+          <a:round/>
+          <a:headEnd/>
+          <a:tailEnd/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>609600</xdr:colOff>
+      <xdr:row>38</xdr:row>
+      <xdr:rowOff>167640</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="3" name="AutoShape 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5A2A296F-C905-DAB9-31B5-A3271C15C919}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="7620000" cy="7620000"/>
+        </a:xfrm>
+        <a:custGeom>
+          <a:avLst/>
+          <a:gdLst/>
+          <a:ahLst/>
+          <a:cxnLst/>
+          <a:rect l="0" t="0" r="0" b="0"/>
+          <a:pathLst/>
+        </a:custGeom>
+        <a:solidFill>
+          <a:srgbClr val="FFFFFF"/>
+        </a:solidFill>
+        <a:ln w="9525">
+          <a:solidFill>
+            <a:srgbClr val="000000"/>
+          </a:solidFill>
+          <a:round/>
+          <a:headEnd/>
+          <a:tailEnd/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>609600</xdr:colOff>
+      <xdr:row>38</xdr:row>
+      <xdr:rowOff>167640</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="4" name="AutoShape 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2019BF22-4544-A1A8-E3E7-5BB82199161C}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="7620000" cy="7620000"/>
+        </a:xfrm>
+        <a:custGeom>
+          <a:avLst/>
+          <a:gdLst/>
+          <a:ahLst/>
+          <a:cxnLst/>
+          <a:rect l="0" t="0" r="0" b="0"/>
+          <a:pathLst/>
+        </a:custGeom>
+        <a:solidFill>
+          <a:srgbClr val="FFFFFF"/>
+        </a:solidFill>
+        <a:ln w="9525">
+          <a:solidFill>
+            <a:srgbClr val="000000"/>
+          </a:solidFill>
+          <a:round/>
+          <a:headEnd/>
+          <a:tailEnd/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>609600</xdr:colOff>
+      <xdr:row>38</xdr:row>
+      <xdr:rowOff>167640</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="5" name="AutoShape 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E945B8FC-64BC-DC4E-5861-E5116935EA6C}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -5137,293 +5461,308 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8">
-      <c r="A1" s="146" t="s">
+      <c r="A1" s="133" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="146"/>
-      <c r="C1" s="146"/>
-      <c r="D1" s="146"/>
-      <c r="E1" s="146"/>
-      <c r="F1" s="146"/>
-      <c r="G1" s="146"/>
-      <c r="H1" s="146"/>
+      <c r="B1" s="133"/>
+      <c r="C1" s="133"/>
+      <c r="D1" s="133"/>
+      <c r="E1" s="133"/>
+      <c r="F1" s="133"/>
+      <c r="G1" s="133"/>
+      <c r="H1" s="133"/>
     </row>
     <row r="2" spans="1:8">
-      <c r="A2" s="146"/>
-      <c r="B2" s="146"/>
-      <c r="C2" s="146"/>
-      <c r="D2" s="146"/>
-      <c r="E2" s="146"/>
-      <c r="F2" s="146"/>
-      <c r="G2" s="146"/>
-      <c r="H2" s="146"/>
+      <c r="A2" s="133"/>
+      <c r="B2" s="133"/>
+      <c r="C2" s="133"/>
+      <c r="D2" s="133"/>
+      <c r="E2" s="133"/>
+      <c r="F2" s="133"/>
+      <c r="G2" s="133"/>
+      <c r="H2" s="133"/>
     </row>
     <row r="3" spans="1:8">
-      <c r="A3" s="147" t="s">
-        <v>1</v>
-      </c>
-      <c r="B3" s="147"/>
-      <c r="C3" s="147"/>
-      <c r="D3" s="147"/>
-      <c r="E3" s="147"/>
-      <c r="F3" s="147"/>
-      <c r="G3" s="147"/>
-      <c r="H3" s="147"/>
+      <c r="A3" s="134" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" s="134"/>
+      <c r="C3" s="134"/>
+      <c r="D3" s="134"/>
+      <c r="E3" s="134"/>
+      <c r="F3" s="134"/>
+      <c r="G3" s="134"/>
+      <c r="H3" s="134"/>
     </row>
     <row r="5" spans="1:8">
-      <c r="A5" s="148" t="s">
+      <c r="A5" s="135" t="s">
         <v>2</v>
       </c>
-      <c r="B5" s="148"/>
-      <c r="C5" s="148" t="s">
+      <c r="B5" s="135"/>
+      <c r="C5" s="135" t="s">
         <v>3</v>
       </c>
-      <c r="D5" s="148"/>
-      <c r="E5" s="148" t="s">
+      <c r="D5" s="135"/>
+      <c r="E5" s="135" t="s">
         <v>4</v>
       </c>
-      <c r="F5" s="148"/>
-      <c r="G5" s="148" t="s">
+      <c r="F5" s="135"/>
+      <c r="G5" s="135" t="s">
         <v>5</v>
       </c>
-      <c r="H5" s="148"/>
+      <c r="H5" s="135"/>
     </row>
     <row r="6" spans="1:8">
-      <c r="A6" s="149" t="str">
+      <c r="A6" s="136" t="str">
         <f>IF(COUNTIF(QA_Checks!$E$2:$E$16,"FAIL")=0,"READY TO RUN","REVIEW REQUIRED")</f>
         <v>REVIEW REQUIRED</v>
       </c>
-      <c r="B6" s="150"/>
-      <c r="C6" s="149">
+      <c r="B6" s="137"/>
+      <c r="C6" s="136">
         <f>COUNTA(Dictionaries!$A$2:$A$8)</f>
         <v>7</v>
       </c>
-      <c r="D6" s="150"/>
-      <c r="E6" s="149">
+      <c r="D6" s="137"/>
+      <c r="E6" s="136">
         <f>COUNTA(Dictionaries!$F$2:$F$6)</f>
         <v>5</v>
       </c>
-      <c r="F6" s="150"/>
-      <c r="G6" s="149">
+      <c r="F6" s="137"/>
+      <c r="G6" s="136">
         <f>COUNTA(Intervention_Cause_Map!$A$2:$A$29)</f>
         <v>28</v>
       </c>
-      <c r="H6" s="150"/>
+      <c r="H6" s="137"/>
     </row>
     <row r="7" spans="1:8">
-      <c r="A7" s="151"/>
-      <c r="B7" s="152"/>
-      <c r="C7" s="151"/>
-      <c r="D7" s="152"/>
-      <c r="E7" s="151"/>
-      <c r="F7" s="152"/>
-      <c r="G7" s="151"/>
-      <c r="H7" s="152"/>
+      <c r="A7" s="138"/>
+      <c r="B7" s="139"/>
+      <c r="C7" s="138"/>
+      <c r="D7" s="139"/>
+      <c r="E7" s="138"/>
+      <c r="F7" s="139"/>
+      <c r="G7" s="138"/>
+      <c r="H7" s="139"/>
     </row>
     <row r="9" spans="1:8">
-      <c r="A9" s="138" t="s">
+      <c r="A9" s="140" t="s">
         <v>6</v>
       </c>
-      <c r="B9" s="138"/>
-      <c r="C9" s="138"/>
-      <c r="D9" s="138"/>
-      <c r="E9" s="138"/>
-      <c r="F9" s="138"/>
-      <c r="G9" s="138"/>
-      <c r="H9" s="138"/>
+      <c r="B9" s="140"/>
+      <c r="C9" s="140"/>
+      <c r="D9" s="140"/>
+      <c r="E9" s="140"/>
+      <c r="F9" s="140"/>
+      <c r="G9" s="140"/>
+      <c r="H9" s="140"/>
     </row>
     <row r="10" spans="1:8" ht="28.05" customHeight="1">
       <c r="A10" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="B10" s="140" t="s">
+      <c r="B10" s="141" t="s">
         <v>8</v>
       </c>
-      <c r="C10" s="141"/>
-      <c r="D10" s="141"/>
-      <c r="E10" s="141"/>
-      <c r="F10" s="141"/>
-      <c r="G10" s="141"/>
-      <c r="H10" s="142"/>
+      <c r="C10" s="142"/>
+      <c r="D10" s="142"/>
+      <c r="E10" s="142"/>
+      <c r="F10" s="142"/>
+      <c r="G10" s="142"/>
+      <c r="H10" s="143"/>
     </row>
     <row r="11" spans="1:8" ht="28.05" customHeight="1">
       <c r="A11" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="B11" s="143" t="s">
+      <c r="B11" s="144" t="s">
         <v>10</v>
       </c>
-      <c r="C11" s="144"/>
-      <c r="D11" s="144"/>
-      <c r="E11" s="144"/>
-      <c r="F11" s="144"/>
-      <c r="G11" s="144"/>
-      <c r="H11" s="145"/>
+      <c r="C11" s="145"/>
+      <c r="D11" s="145"/>
+      <c r="E11" s="145"/>
+      <c r="F11" s="145"/>
+      <c r="G11" s="145"/>
+      <c r="H11" s="146"/>
     </row>
     <row r="12" spans="1:8" ht="28.05" customHeight="1">
       <c r="A12" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="B12" s="143" t="s">
+      <c r="B12" s="144" t="s">
         <v>12</v>
       </c>
-      <c r="C12" s="144"/>
-      <c r="D12" s="144"/>
-      <c r="E12" s="144"/>
-      <c r="F12" s="144"/>
-      <c r="G12" s="144"/>
-      <c r="H12" s="145"/>
+      <c r="C12" s="145"/>
+      <c r="D12" s="145"/>
+      <c r="E12" s="145"/>
+      <c r="F12" s="145"/>
+      <c r="G12" s="145"/>
+      <c r="H12" s="146"/>
     </row>
     <row r="13" spans="1:8" ht="28.05" customHeight="1">
       <c r="A13" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="B13" s="143" t="s">
+      <c r="B13" s="144" t="s">
         <v>14</v>
       </c>
-      <c r="C13" s="144"/>
-      <c r="D13" s="144"/>
-      <c r="E13" s="144"/>
-      <c r="F13" s="144"/>
-      <c r="G13" s="144"/>
-      <c r="H13" s="145"/>
+      <c r="C13" s="145"/>
+      <c r="D13" s="145"/>
+      <c r="E13" s="145"/>
+      <c r="F13" s="145"/>
+      <c r="G13" s="145"/>
+      <c r="H13" s="146"/>
     </row>
     <row r="14" spans="1:8" ht="28.05" customHeight="1">
       <c r="A14" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="B14" s="135" t="s">
+      <c r="B14" s="147" t="s">
         <v>16</v>
       </c>
-      <c r="C14" s="136"/>
-      <c r="D14" s="136"/>
-      <c r="E14" s="136"/>
-      <c r="F14" s="136"/>
-      <c r="G14" s="136"/>
-      <c r="H14" s="137"/>
+      <c r="C14" s="148"/>
+      <c r="D14" s="148"/>
+      <c r="E14" s="148"/>
+      <c r="F14" s="148"/>
+      <c r="G14" s="148"/>
+      <c r="H14" s="149"/>
     </row>
     <row r="17" spans="1:8">
-      <c r="A17" s="138" t="s">
+      <c r="A17" s="140" t="s">
         <v>17</v>
       </c>
-      <c r="B17" s="138"/>
-      <c r="C17" s="138"/>
-      <c r="D17" s="138"/>
-      <c r="E17" s="138"/>
-      <c r="F17" s="138"/>
-      <c r="G17" s="138"/>
-      <c r="H17" s="138"/>
+      <c r="B17" s="140"/>
+      <c r="C17" s="140"/>
+      <c r="D17" s="140"/>
+      <c r="E17" s="140"/>
+      <c r="F17" s="140"/>
+      <c r="G17" s="140"/>
+      <c r="H17" s="140"/>
     </row>
     <row r="18" spans="1:8" ht="27" customHeight="1">
       <c r="A18" s="48" t="s">
         <v>18</v>
       </c>
-      <c r="B18" s="133" t="s">
+      <c r="B18" s="150" t="s">
         <v>19</v>
       </c>
-      <c r="C18" s="133"/>
-      <c r="D18" s="133"/>
-      <c r="E18" s="133"/>
-      <c r="F18" s="133"/>
-      <c r="G18" s="133"/>
-      <c r="H18" s="133"/>
+      <c r="C18" s="150"/>
+      <c r="D18" s="150"/>
+      <c r="E18" s="150"/>
+      <c r="F18" s="150"/>
+      <c r="G18" s="150"/>
+      <c r="H18" s="150"/>
     </row>
     <row r="19" spans="1:8" ht="27" customHeight="1">
       <c r="A19" s="48" t="s">
         <v>18</v>
       </c>
-      <c r="B19" s="133" t="s">
+      <c r="B19" s="150" t="s">
         <v>20</v>
       </c>
-      <c r="C19" s="133"/>
-      <c r="D19" s="133"/>
-      <c r="E19" s="133"/>
-      <c r="F19" s="133"/>
-      <c r="G19" s="133"/>
-      <c r="H19" s="133"/>
+      <c r="C19" s="150"/>
+      <c r="D19" s="150"/>
+      <c r="E19" s="150"/>
+      <c r="F19" s="150"/>
+      <c r="G19" s="150"/>
+      <c r="H19" s="150"/>
     </row>
     <row r="20" spans="1:8" ht="27" customHeight="1">
       <c r="A20" s="47" t="s">
         <v>21</v>
       </c>
-      <c r="B20" s="139" t="s">
+      <c r="B20" s="151" t="s">
         <v>22</v>
       </c>
-      <c r="C20" s="133"/>
-      <c r="D20" s="133"/>
-      <c r="E20" s="133"/>
-      <c r="F20" s="133"/>
-      <c r="G20" s="133"/>
-      <c r="H20" s="133"/>
+      <c r="C20" s="150"/>
+      <c r="D20" s="150"/>
+      <c r="E20" s="150"/>
+      <c r="F20" s="150"/>
+      <c r="G20" s="150"/>
+      <c r="H20" s="150"/>
     </row>
     <row r="21" spans="1:8" ht="27" customHeight="1">
       <c r="A21" s="48" t="s">
         <v>21</v>
       </c>
-      <c r="B21" s="133" t="s">
+      <c r="B21" s="150" t="s">
         <v>23</v>
       </c>
-      <c r="C21" s="133"/>
-      <c r="D21" s="133"/>
-      <c r="E21" s="133"/>
-      <c r="F21" s="133"/>
-      <c r="G21" s="133"/>
-      <c r="H21" s="133"/>
+      <c r="C21" s="150"/>
+      <c r="D21" s="150"/>
+      <c r="E21" s="150"/>
+      <c r="F21" s="150"/>
+      <c r="G21" s="150"/>
+      <c r="H21" s="150"/>
     </row>
     <row r="22" spans="1:8" ht="27" customHeight="1">
       <c r="A22" s="48" t="s">
         <v>24</v>
       </c>
-      <c r="B22" s="133" t="s">
+      <c r="B22" s="150" t="s">
         <v>25</v>
       </c>
-      <c r="C22" s="133"/>
-      <c r="D22" s="133"/>
-      <c r="E22" s="133"/>
-      <c r="F22" s="133"/>
-      <c r="G22" s="133"/>
-      <c r="H22" s="133"/>
+      <c r="C22" s="150"/>
+      <c r="D22" s="150"/>
+      <c r="E22" s="150"/>
+      <c r="F22" s="150"/>
+      <c r="G22" s="150"/>
+      <c r="H22" s="150"/>
     </row>
     <row r="23" spans="1:8" ht="27" customHeight="1">
       <c r="A23" s="48" t="s">
         <v>26</v>
       </c>
-      <c r="B23" s="133" t="s">
+      <c r="B23" s="150" t="s">
         <v>27</v>
       </c>
-      <c r="C23" s="133"/>
-      <c r="D23" s="133"/>
-      <c r="E23" s="133"/>
-      <c r="F23" s="133"/>
-      <c r="G23" s="133"/>
-      <c r="H23" s="133"/>
+      <c r="C23" s="150"/>
+      <c r="D23" s="150"/>
+      <c r="E23" s="150"/>
+      <c r="F23" s="150"/>
+      <c r="G23" s="150"/>
+      <c r="H23" s="150"/>
     </row>
     <row r="24" spans="1:8" ht="27" customHeight="1">
       <c r="A24" s="48" t="s">
         <v>28</v>
       </c>
-      <c r="B24" s="133" t="s">
+      <c r="B24" s="150" t="s">
         <v>29</v>
       </c>
-      <c r="C24" s="133"/>
-      <c r="D24" s="133"/>
-      <c r="E24" s="133"/>
-      <c r="F24" s="133"/>
-      <c r="G24" s="133"/>
-      <c r="H24" s="133"/>
+      <c r="C24" s="150"/>
+      <c r="D24" s="150"/>
+      <c r="E24" s="150"/>
+      <c r="F24" s="150"/>
+      <c r="G24" s="150"/>
+      <c r="H24" s="150"/>
     </row>
     <row r="26" spans="1:8">
-      <c r="A26" s="134"/>
-      <c r="B26" s="134"/>
-      <c r="C26" s="134"/>
-      <c r="D26" s="134"/>
-      <c r="E26" s="134"/>
-      <c r="F26" s="134"/>
-      <c r="G26" s="134"/>
-      <c r="H26" s="134"/>
+      <c r="A26" s="152"/>
+      <c r="B26" s="152"/>
+      <c r="C26" s="152"/>
+      <c r="D26" s="152"/>
+      <c r="E26" s="152"/>
+      <c r="F26" s="152"/>
+      <c r="G26" s="152"/>
+      <c r="H26" s="152"/>
     </row>
   </sheetData>
   <mergeCells count="25">
+    <mergeCell ref="B21:H21"/>
+    <mergeCell ref="B22:H22"/>
+    <mergeCell ref="B23:H23"/>
+    <mergeCell ref="B24:H24"/>
+    <mergeCell ref="A26:H26"/>
+    <mergeCell ref="B14:H14"/>
+    <mergeCell ref="A17:H17"/>
+    <mergeCell ref="B18:H18"/>
+    <mergeCell ref="B19:H19"/>
+    <mergeCell ref="B20:H20"/>
+    <mergeCell ref="A9:H9"/>
+    <mergeCell ref="B10:H10"/>
+    <mergeCell ref="B11:H11"/>
+    <mergeCell ref="B12:H12"/>
+    <mergeCell ref="B13:H13"/>
     <mergeCell ref="A1:H2"/>
     <mergeCell ref="A3:H3"/>
     <mergeCell ref="A5:B5"/>
@@ -5434,21 +5773,6 @@
     <mergeCell ref="E6:F7"/>
     <mergeCell ref="G5:H5"/>
     <mergeCell ref="G6:H7"/>
-    <mergeCell ref="A9:H9"/>
-    <mergeCell ref="B10:H10"/>
-    <mergeCell ref="B11:H11"/>
-    <mergeCell ref="B12:H12"/>
-    <mergeCell ref="B13:H13"/>
-    <mergeCell ref="B14:H14"/>
-    <mergeCell ref="A17:H17"/>
-    <mergeCell ref="B18:H18"/>
-    <mergeCell ref="B19:H19"/>
-    <mergeCell ref="B20:H20"/>
-    <mergeCell ref="B21:H21"/>
-    <mergeCell ref="B22:H22"/>
-    <mergeCell ref="B23:H23"/>
-    <mergeCell ref="B24:H24"/>
-    <mergeCell ref="A26:H26"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/data/indonesia_model_inputs_public_health.xlsx
+++ b/data/indonesia_model_inputs_public_health.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://uwnetid-my.sharepoint.com/personal/wrgg_uw_edu/Documents/02Work/WorldBank-Indonesia/uw-wb-indonesia-ncd/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="58" documentId="11_4329EEFB852386115C62C6D576342767CA1B238E" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3135964A-B0BD-4C55-A8F1-78CE430B8713}"/>
+  <xr:revisionPtr revIDLastSave="65" documentId="11_4329EEFB852386115C62C6D576342767CA1B238E" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{74B92C35-2AD0-4E00-BA2D-FF148BE7E351}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="4" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="README" sheetId="1" r:id="rId1"/>
@@ -3550,6 +3550,43 @@
     <xf numFmtId="164" fontId="18" fillId="7" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -3570,43 +3607,6 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -4644,6 +4644,168 @@
     </xdr:sp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>609600</xdr:colOff>
+      <xdr:row>33</xdr:row>
+      <xdr:rowOff>7620</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="6" name="AutoShape 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FE33A526-33E0-5575-8211-8B31825F82FC}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="7620000" cy="6797040"/>
+        </a:xfrm>
+        <a:custGeom>
+          <a:avLst/>
+          <a:gdLst/>
+          <a:ahLst/>
+          <a:cxnLst/>
+          <a:rect l="0" t="0" r="0" b="0"/>
+          <a:pathLst/>
+        </a:custGeom>
+        <a:solidFill>
+          <a:srgbClr val="FFFFFF"/>
+        </a:solidFill>
+        <a:ln w="9525">
+          <a:solidFill>
+            <a:srgbClr val="000000"/>
+          </a:solidFill>
+          <a:round/>
+          <a:headEnd/>
+          <a:tailEnd/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>609600</xdr:colOff>
+      <xdr:row>33</xdr:row>
+      <xdr:rowOff>7620</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="7" name="AutoShape 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E193280C-EC07-0880-2016-95627938E0D8}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="7620000" cy="6797040"/>
+        </a:xfrm>
+        <a:custGeom>
+          <a:avLst/>
+          <a:gdLst/>
+          <a:ahLst/>
+          <a:cxnLst/>
+          <a:rect l="0" t="0" r="0" b="0"/>
+          <a:pathLst/>
+        </a:custGeom>
+        <a:solidFill>
+          <a:srgbClr val="FFFFFF"/>
+        </a:solidFill>
+        <a:ln w="9525">
+          <a:solidFill>
+            <a:srgbClr val="000000"/>
+          </a:solidFill>
+          <a:round/>
+          <a:headEnd/>
+          <a:tailEnd/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>609600</xdr:colOff>
+      <xdr:row>33</xdr:row>
+      <xdr:rowOff>7620</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="8" name="AutoShape 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DCDCAA57-50AD-6C6E-BB99-3438BCA1CF97}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="7620000" cy="6797040"/>
+        </a:xfrm>
+        <a:custGeom>
+          <a:avLst/>
+          <a:gdLst/>
+          <a:ahLst/>
+          <a:cxnLst/>
+          <a:rect l="0" t="0" r="0" b="0"/>
+          <a:pathLst/>
+        </a:custGeom>
+        <a:solidFill>
+          <a:srgbClr val="FFFFFF"/>
+        </a:solidFill>
+        <a:ln w="9525">
+          <a:solidFill>
+            <a:srgbClr val="000000"/>
+          </a:solidFill>
+          <a:round/>
+          <a:headEnd/>
+          <a:tailEnd/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
 </xdr:wsDr>
 </file>
 
@@ -4879,6 +5041,168 @@
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
               <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E945B8FC-64BC-DC4E-5861-E5116935EA6C}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="7620000" cy="7620000"/>
+        </a:xfrm>
+        <a:custGeom>
+          <a:avLst/>
+          <a:gdLst/>
+          <a:ahLst/>
+          <a:cxnLst/>
+          <a:rect l="0" t="0" r="0" b="0"/>
+          <a:pathLst/>
+        </a:custGeom>
+        <a:solidFill>
+          <a:srgbClr val="FFFFFF"/>
+        </a:solidFill>
+        <a:ln w="9525">
+          <a:solidFill>
+            <a:srgbClr val="000000"/>
+          </a:solidFill>
+          <a:round/>
+          <a:headEnd/>
+          <a:tailEnd/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>609600</xdr:colOff>
+      <xdr:row>38</xdr:row>
+      <xdr:rowOff>167640</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="6" name="AutoShape 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F49600E0-4750-0ED2-0C63-99D5EA0C30B9}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="7620000" cy="7620000"/>
+        </a:xfrm>
+        <a:custGeom>
+          <a:avLst/>
+          <a:gdLst/>
+          <a:ahLst/>
+          <a:cxnLst/>
+          <a:rect l="0" t="0" r="0" b="0"/>
+          <a:pathLst/>
+        </a:custGeom>
+        <a:solidFill>
+          <a:srgbClr val="FFFFFF"/>
+        </a:solidFill>
+        <a:ln w="9525">
+          <a:solidFill>
+            <a:srgbClr val="000000"/>
+          </a:solidFill>
+          <a:round/>
+          <a:headEnd/>
+          <a:tailEnd/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>609600</xdr:colOff>
+      <xdr:row>38</xdr:row>
+      <xdr:rowOff>167640</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="7" name="AutoShape 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7B329269-3250-C64B-308E-559A3F849E34}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="7620000" cy="7620000"/>
+        </a:xfrm>
+        <a:custGeom>
+          <a:avLst/>
+          <a:gdLst/>
+          <a:ahLst/>
+          <a:cxnLst/>
+          <a:rect l="0" t="0" r="0" b="0"/>
+          <a:pathLst/>
+        </a:custGeom>
+        <a:solidFill>
+          <a:srgbClr val="FFFFFF"/>
+        </a:solidFill>
+        <a:ln w="9525">
+          <a:solidFill>
+            <a:srgbClr val="000000"/>
+          </a:solidFill>
+          <a:round/>
+          <a:headEnd/>
+          <a:tailEnd/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>609600</xdr:colOff>
+      <xdr:row>38</xdr:row>
+      <xdr:rowOff>167640</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="8" name="AutoShape 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{19D700C8-6823-48CF-D892-0A1D00654CC6}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -5461,308 +5785,293 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8">
-      <c r="A1" s="133" t="s">
+      <c r="A1" s="146" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="133"/>
-      <c r="C1" s="133"/>
-      <c r="D1" s="133"/>
-      <c r="E1" s="133"/>
-      <c r="F1" s="133"/>
-      <c r="G1" s="133"/>
-      <c r="H1" s="133"/>
+      <c r="B1" s="146"/>
+      <c r="C1" s="146"/>
+      <c r="D1" s="146"/>
+      <c r="E1" s="146"/>
+      <c r="F1" s="146"/>
+      <c r="G1" s="146"/>
+      <c r="H1" s="146"/>
     </row>
     <row r="2" spans="1:8">
-      <c r="A2" s="133"/>
-      <c r="B2" s="133"/>
-      <c r="C2" s="133"/>
-      <c r="D2" s="133"/>
-      <c r="E2" s="133"/>
-      <c r="F2" s="133"/>
-      <c r="G2" s="133"/>
-      <c r="H2" s="133"/>
+      <c r="A2" s="146"/>
+      <c r="B2" s="146"/>
+      <c r="C2" s="146"/>
+      <c r="D2" s="146"/>
+      <c r="E2" s="146"/>
+      <c r="F2" s="146"/>
+      <c r="G2" s="146"/>
+      <c r="H2" s="146"/>
     </row>
     <row r="3" spans="1:8">
-      <c r="A3" s="134" t="s">
-        <v>1</v>
-      </c>
-      <c r="B3" s="134"/>
-      <c r="C3" s="134"/>
-      <c r="D3" s="134"/>
-      <c r="E3" s="134"/>
-      <c r="F3" s="134"/>
-      <c r="G3" s="134"/>
-      <c r="H3" s="134"/>
+      <c r="A3" s="147" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" s="147"/>
+      <c r="C3" s="147"/>
+      <c r="D3" s="147"/>
+      <c r="E3" s="147"/>
+      <c r="F3" s="147"/>
+      <c r="G3" s="147"/>
+      <c r="H3" s="147"/>
     </row>
     <row r="5" spans="1:8">
-      <c r="A5" s="135" t="s">
+      <c r="A5" s="148" t="s">
         <v>2</v>
       </c>
-      <c r="B5" s="135"/>
-      <c r="C5" s="135" t="s">
+      <c r="B5" s="148"/>
+      <c r="C5" s="148" t="s">
         <v>3</v>
       </c>
-      <c r="D5" s="135"/>
-      <c r="E5" s="135" t="s">
+      <c r="D5" s="148"/>
+      <c r="E5" s="148" t="s">
         <v>4</v>
       </c>
-      <c r="F5" s="135"/>
-      <c r="G5" s="135" t="s">
+      <c r="F5" s="148"/>
+      <c r="G5" s="148" t="s">
         <v>5</v>
       </c>
-      <c r="H5" s="135"/>
+      <c r="H5" s="148"/>
     </row>
     <row r="6" spans="1:8">
-      <c r="A6" s="136" t="str">
+      <c r="A6" s="149" t="str">
         <f>IF(COUNTIF(QA_Checks!$E$2:$E$16,"FAIL")=0,"READY TO RUN","REVIEW REQUIRED")</f>
         <v>REVIEW REQUIRED</v>
       </c>
-      <c r="B6" s="137"/>
-      <c r="C6" s="136">
+      <c r="B6" s="150"/>
+      <c r="C6" s="149">
         <f>COUNTA(Dictionaries!$A$2:$A$8)</f>
         <v>7</v>
       </c>
-      <c r="D6" s="137"/>
-      <c r="E6" s="136">
+      <c r="D6" s="150"/>
+      <c r="E6" s="149">
         <f>COUNTA(Dictionaries!$F$2:$F$6)</f>
         <v>5</v>
       </c>
-      <c r="F6" s="137"/>
-      <c r="G6" s="136">
+      <c r="F6" s="150"/>
+      <c r="G6" s="149">
         <f>COUNTA(Intervention_Cause_Map!$A$2:$A$29)</f>
         <v>28</v>
       </c>
-      <c r="H6" s="137"/>
+      <c r="H6" s="150"/>
     </row>
     <row r="7" spans="1:8">
-      <c r="A7" s="138"/>
-      <c r="B7" s="139"/>
-      <c r="C7" s="138"/>
-      <c r="D7" s="139"/>
-      <c r="E7" s="138"/>
-      <c r="F7" s="139"/>
-      <c r="G7" s="138"/>
-      <c r="H7" s="139"/>
+      <c r="A7" s="151"/>
+      <c r="B7" s="152"/>
+      <c r="C7" s="151"/>
+      <c r="D7" s="152"/>
+      <c r="E7" s="151"/>
+      <c r="F7" s="152"/>
+      <c r="G7" s="151"/>
+      <c r="H7" s="152"/>
     </row>
     <row r="9" spans="1:8">
-      <c r="A9" s="140" t="s">
+      <c r="A9" s="138" t="s">
         <v>6</v>
       </c>
-      <c r="B9" s="140"/>
-      <c r="C9" s="140"/>
-      <c r="D9" s="140"/>
-      <c r="E9" s="140"/>
-      <c r="F9" s="140"/>
-      <c r="G9" s="140"/>
-      <c r="H9" s="140"/>
+      <c r="B9" s="138"/>
+      <c r="C9" s="138"/>
+      <c r="D9" s="138"/>
+      <c r="E9" s="138"/>
+      <c r="F9" s="138"/>
+      <c r="G9" s="138"/>
+      <c r="H9" s="138"/>
     </row>
     <row r="10" spans="1:8" ht="28.05" customHeight="1">
       <c r="A10" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="B10" s="141" t="s">
+      <c r="B10" s="140" t="s">
         <v>8</v>
       </c>
-      <c r="C10" s="142"/>
-      <c r="D10" s="142"/>
-      <c r="E10" s="142"/>
-      <c r="F10" s="142"/>
-      <c r="G10" s="142"/>
-      <c r="H10" s="143"/>
+      <c r="C10" s="141"/>
+      <c r="D10" s="141"/>
+      <c r="E10" s="141"/>
+      <c r="F10" s="141"/>
+      <c r="G10" s="141"/>
+      <c r="H10" s="142"/>
     </row>
     <row r="11" spans="1:8" ht="28.05" customHeight="1">
       <c r="A11" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="B11" s="144" t="s">
+      <c r="B11" s="143" t="s">
         <v>10</v>
       </c>
-      <c r="C11" s="145"/>
-      <c r="D11" s="145"/>
-      <c r="E11" s="145"/>
-      <c r="F11" s="145"/>
-      <c r="G11" s="145"/>
-      <c r="H11" s="146"/>
+      <c r="C11" s="144"/>
+      <c r="D11" s="144"/>
+      <c r="E11" s="144"/>
+      <c r="F11" s="144"/>
+      <c r="G11" s="144"/>
+      <c r="H11" s="145"/>
     </row>
     <row r="12" spans="1:8" ht="28.05" customHeight="1">
       <c r="A12" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="B12" s="144" t="s">
+      <c r="B12" s="143" t="s">
         <v>12</v>
       </c>
-      <c r="C12" s="145"/>
-      <c r="D12" s="145"/>
-      <c r="E12" s="145"/>
-      <c r="F12" s="145"/>
-      <c r="G12" s="145"/>
-      <c r="H12" s="146"/>
+      <c r="C12" s="144"/>
+      <c r="D12" s="144"/>
+      <c r="E12" s="144"/>
+      <c r="F12" s="144"/>
+      <c r="G12" s="144"/>
+      <c r="H12" s="145"/>
     </row>
     <row r="13" spans="1:8" ht="28.05" customHeight="1">
       <c r="A13" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="B13" s="144" t="s">
+      <c r="B13" s="143" t="s">
         <v>14</v>
       </c>
-      <c r="C13" s="145"/>
-      <c r="D13" s="145"/>
-      <c r="E13" s="145"/>
-      <c r="F13" s="145"/>
-      <c r="G13" s="145"/>
-      <c r="H13" s="146"/>
+      <c r="C13" s="144"/>
+      <c r="D13" s="144"/>
+      <c r="E13" s="144"/>
+      <c r="F13" s="144"/>
+      <c r="G13" s="144"/>
+      <c r="H13" s="145"/>
     </row>
     <row r="14" spans="1:8" ht="28.05" customHeight="1">
       <c r="A14" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="B14" s="147" t="s">
+      <c r="B14" s="135" t="s">
         <v>16</v>
       </c>
-      <c r="C14" s="148"/>
-      <c r="D14" s="148"/>
-      <c r="E14" s="148"/>
-      <c r="F14" s="148"/>
-      <c r="G14" s="148"/>
-      <c r="H14" s="149"/>
+      <c r="C14" s="136"/>
+      <c r="D14" s="136"/>
+      <c r="E14" s="136"/>
+      <c r="F14" s="136"/>
+      <c r="G14" s="136"/>
+      <c r="H14" s="137"/>
     </row>
     <row r="17" spans="1:8">
-      <c r="A17" s="140" t="s">
+      <c r="A17" s="138" t="s">
         <v>17</v>
       </c>
-      <c r="B17" s="140"/>
-      <c r="C17" s="140"/>
-      <c r="D17" s="140"/>
-      <c r="E17" s="140"/>
-      <c r="F17" s="140"/>
-      <c r="G17" s="140"/>
-      <c r="H17" s="140"/>
+      <c r="B17" s="138"/>
+      <c r="C17" s="138"/>
+      <c r="D17" s="138"/>
+      <c r="E17" s="138"/>
+      <c r="F17" s="138"/>
+      <c r="G17" s="138"/>
+      <c r="H17" s="138"/>
     </row>
     <row r="18" spans="1:8" ht="27" customHeight="1">
       <c r="A18" s="48" t="s">
         <v>18</v>
       </c>
-      <c r="B18" s="150" t="s">
+      <c r="B18" s="133" t="s">
         <v>19</v>
       </c>
-      <c r="C18" s="150"/>
-      <c r="D18" s="150"/>
-      <c r="E18" s="150"/>
-      <c r="F18" s="150"/>
-      <c r="G18" s="150"/>
-      <c r="H18" s="150"/>
+      <c r="C18" s="133"/>
+      <c r="D18" s="133"/>
+      <c r="E18" s="133"/>
+      <c r="F18" s="133"/>
+      <c r="G18" s="133"/>
+      <c r="H18" s="133"/>
     </row>
     <row r="19" spans="1:8" ht="27" customHeight="1">
       <c r="A19" s="48" t="s">
         <v>18</v>
       </c>
-      <c r="B19" s="150" t="s">
+      <c r="B19" s="133" t="s">
         <v>20</v>
       </c>
-      <c r="C19" s="150"/>
-      <c r="D19" s="150"/>
-      <c r="E19" s="150"/>
-      <c r="F19" s="150"/>
-      <c r="G19" s="150"/>
-      <c r="H19" s="150"/>
+      <c r="C19" s="133"/>
+      <c r="D19" s="133"/>
+      <c r="E19" s="133"/>
+      <c r="F19" s="133"/>
+      <c r="G19" s="133"/>
+      <c r="H19" s="133"/>
     </row>
     <row r="20" spans="1:8" ht="27" customHeight="1">
       <c r="A20" s="47" t="s">
         <v>21</v>
       </c>
-      <c r="B20" s="151" t="s">
+      <c r="B20" s="139" t="s">
         <v>22</v>
       </c>
-      <c r="C20" s="150"/>
-      <c r="D20" s="150"/>
-      <c r="E20" s="150"/>
-      <c r="F20" s="150"/>
-      <c r="G20" s="150"/>
-      <c r="H20" s="150"/>
+      <c r="C20" s="133"/>
+      <c r="D20" s="133"/>
+      <c r="E20" s="133"/>
+      <c r="F20" s="133"/>
+      <c r="G20" s="133"/>
+      <c r="H20" s="133"/>
     </row>
     <row r="21" spans="1:8" ht="27" customHeight="1">
       <c r="A21" s="48" t="s">
         <v>21</v>
       </c>
-      <c r="B21" s="150" t="s">
+      <c r="B21" s="133" t="s">
         <v>23</v>
       </c>
-      <c r="C21" s="150"/>
-      <c r="D21" s="150"/>
-      <c r="E21" s="150"/>
-      <c r="F21" s="150"/>
-      <c r="G21" s="150"/>
-      <c r="H21" s="150"/>
+      <c r="C21" s="133"/>
+      <c r="D21" s="133"/>
+      <c r="E21" s="133"/>
+      <c r="F21" s="133"/>
+      <c r="G21" s="133"/>
+      <c r="H21" s="133"/>
     </row>
     <row r="22" spans="1:8" ht="27" customHeight="1">
       <c r="A22" s="48" t="s">
         <v>24</v>
       </c>
-      <c r="B22" s="150" t="s">
+      <c r="B22" s="133" t="s">
         <v>25</v>
       </c>
-      <c r="C22" s="150"/>
-      <c r="D22" s="150"/>
-      <c r="E22" s="150"/>
-      <c r="F22" s="150"/>
-      <c r="G22" s="150"/>
-      <c r="H22" s="150"/>
+      <c r="C22" s="133"/>
+      <c r="D22" s="133"/>
+      <c r="E22" s="133"/>
+      <c r="F22" s="133"/>
+      <c r="G22" s="133"/>
+      <c r="H22" s="133"/>
     </row>
     <row r="23" spans="1:8" ht="27" customHeight="1">
       <c r="A23" s="48" t="s">
         <v>26</v>
       </c>
-      <c r="B23" s="150" t="s">
+      <c r="B23" s="133" t="s">
         <v>27</v>
       </c>
-      <c r="C23" s="150"/>
-      <c r="D23" s="150"/>
-      <c r="E23" s="150"/>
-      <c r="F23" s="150"/>
-      <c r="G23" s="150"/>
-      <c r="H23" s="150"/>
+      <c r="C23" s="133"/>
+      <c r="D23" s="133"/>
+      <c r="E23" s="133"/>
+      <c r="F23" s="133"/>
+      <c r="G23" s="133"/>
+      <c r="H23" s="133"/>
     </row>
     <row r="24" spans="1:8" ht="27" customHeight="1">
       <c r="A24" s="48" t="s">
         <v>28</v>
       </c>
-      <c r="B24" s="150" t="s">
+      <c r="B24" s="133" t="s">
         <v>29</v>
       </c>
-      <c r="C24" s="150"/>
-      <c r="D24" s="150"/>
-      <c r="E24" s="150"/>
-      <c r="F24" s="150"/>
-      <c r="G24" s="150"/>
-      <c r="H24" s="150"/>
+      <c r="C24" s="133"/>
+      <c r="D24" s="133"/>
+      <c r="E24" s="133"/>
+      <c r="F24" s="133"/>
+      <c r="G24" s="133"/>
+      <c r="H24" s="133"/>
     </row>
     <row r="26" spans="1:8">
-      <c r="A26" s="152"/>
-      <c r="B26" s="152"/>
-      <c r="C26" s="152"/>
-      <c r="D26" s="152"/>
-      <c r="E26" s="152"/>
-      <c r="F26" s="152"/>
-      <c r="G26" s="152"/>
-      <c r="H26" s="152"/>
+      <c r="A26" s="134"/>
+      <c r="B26" s="134"/>
+      <c r="C26" s="134"/>
+      <c r="D26" s="134"/>
+      <c r="E26" s="134"/>
+      <c r="F26" s="134"/>
+      <c r="G26" s="134"/>
+      <c r="H26" s="134"/>
     </row>
   </sheetData>
   <mergeCells count="25">
-    <mergeCell ref="B21:H21"/>
-    <mergeCell ref="B22:H22"/>
-    <mergeCell ref="B23:H23"/>
-    <mergeCell ref="B24:H24"/>
-    <mergeCell ref="A26:H26"/>
-    <mergeCell ref="B14:H14"/>
-    <mergeCell ref="A17:H17"/>
-    <mergeCell ref="B18:H18"/>
-    <mergeCell ref="B19:H19"/>
-    <mergeCell ref="B20:H20"/>
-    <mergeCell ref="A9:H9"/>
-    <mergeCell ref="B10:H10"/>
-    <mergeCell ref="B11:H11"/>
-    <mergeCell ref="B12:H12"/>
-    <mergeCell ref="B13:H13"/>
     <mergeCell ref="A1:H2"/>
     <mergeCell ref="A3:H3"/>
     <mergeCell ref="A5:B5"/>
@@ -5773,6 +6082,21 @@
     <mergeCell ref="E6:F7"/>
     <mergeCell ref="G5:H5"/>
     <mergeCell ref="G6:H7"/>
+    <mergeCell ref="A9:H9"/>
+    <mergeCell ref="B10:H10"/>
+    <mergeCell ref="B11:H11"/>
+    <mergeCell ref="B12:H12"/>
+    <mergeCell ref="B13:H13"/>
+    <mergeCell ref="B14:H14"/>
+    <mergeCell ref="A17:H17"/>
+    <mergeCell ref="B18:H18"/>
+    <mergeCell ref="B19:H19"/>
+    <mergeCell ref="B20:H20"/>
+    <mergeCell ref="B21:H21"/>
+    <mergeCell ref="B22:H22"/>
+    <mergeCell ref="B23:H23"/>
+    <mergeCell ref="B24:H24"/>
+    <mergeCell ref="A26:H26"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -5791,14 +6115,15 @@
     <col min="6" max="6" width="14" customWidth="1"/>
     <col min="7" max="7" width="32" customWidth="1"/>
     <col min="8" max="8" width="28" customWidth="1"/>
-    <col min="9" max="9" width="26" customWidth="1"/>
-    <col min="10" max="10" width="46" customWidth="1"/>
-    <col min="11" max="11" width="26" customWidth="1"/>
-    <col min="12" max="13" width="24" customWidth="1"/>
-    <col min="14" max="14" width="18" customWidth="1"/>
-    <col min="15" max="16" width="12" customWidth="1"/>
-    <col min="17" max="17" width="10" customWidth="1"/>
-    <col min="18" max="19" width="18" customWidth="1"/>
+    <col min="9" max="9" width="26" hidden="1" customWidth="1"/>
+    <col min="10" max="10" width="46" hidden="1" customWidth="1"/>
+    <col min="11" max="11" width="26" hidden="1" customWidth="1"/>
+    <col min="12" max="13" width="24" hidden="1" customWidth="1"/>
+    <col min="14" max="14" width="18" hidden="1" customWidth="1"/>
+    <col min="15" max="16" width="12" hidden="1" customWidth="1"/>
+    <col min="17" max="17" width="10" hidden="1" customWidth="1"/>
+    <col min="18" max="18" width="18" hidden="1" customWidth="1"/>
+    <col min="19" max="19" width="18" customWidth="1"/>
     <col min="20" max="20" width="14" customWidth="1"/>
     <col min="21" max="21" width="22" customWidth="1"/>
     <col min="22" max="22" width="18" customWidth="1"/>
@@ -5955,7 +6280,7 @@
         <v>562</v>
       </c>
       <c r="S2" s="42">
-        <v>4.0000000000000001E-3</v>
+        <v>0.04</v>
       </c>
       <c r="T2" s="8">
         <v>2017</v>
@@ -6047,7 +6372,7 @@
         <v>562</v>
       </c>
       <c r="S3" s="43">
-        <v>4.0000000000000001E-3</v>
+        <v>0.04</v>
       </c>
       <c r="T3" s="9">
         <v>2017</v>
@@ -6507,7 +6832,7 @@
         <v>562</v>
       </c>
       <c r="S8" s="43">
-        <v>4.0000000000000001E-3</v>
+        <v>0.04</v>
       </c>
       <c r="T8" s="9">
         <v>2017</v>
@@ -15751,7 +16076,7 @@
       </c>
       <c r="R2" s="94">
         <f>SUMIFS(Cost_Components!$S$2:$S$8,Cost_Components!$G$2:$G$8,P2,Cost_Components!$D$2:$D$8,1)</f>
-        <v>4.0000000000000001E-3</v>
+        <v>0.04</v>
       </c>
       <c r="S2" s="60" t="str">
         <f t="shared" ref="S2:S29" si="2">IF(G2=0,"MISSING EXPOSURE",IF(E2="REVIEW","REVIEW EFFECT",IF(AND(K2="tfa_attributable_ihd_PAF_x_policy_score",M2=""),"REVIEW EFFECT",IF(R2=0,"REVIEW COST","REVIEWED LINK"))))</f>
@@ -15821,7 +16146,7 @@
       </c>
       <c r="R3" s="95">
         <f>SUMIFS(Cost_Components!$S$2:$S$8,Cost_Components!$G$2:$G$8,P3,Cost_Components!$D$2:$D$8,1)</f>
-        <v>4.0000000000000001E-3</v>
+        <v>0.04</v>
       </c>
       <c r="S3" s="62" t="str">
         <f t="shared" si="2"/>
@@ -15891,7 +16216,7 @@
       </c>
       <c r="R4" s="96">
         <f>SUMIFS(Cost_Components!$S$2:$S$8,Cost_Components!$G$2:$G$8,P4,Cost_Components!$D$2:$D$8,1)</f>
-        <v>4.0000000000000001E-3</v>
+        <v>0.04</v>
       </c>
       <c r="S4" s="64" t="str">
         <f t="shared" si="2"/>
@@ -15961,7 +16286,7 @@
       </c>
       <c r="R5" s="95">
         <f>SUMIFS(Cost_Components!$S$2:$S$8,Cost_Components!$G$2:$G$8,P5,Cost_Components!$D$2:$D$8,1)</f>
-        <v>4.0000000000000001E-3</v>
+        <v>0.04</v>
       </c>
       <c r="S5" s="62" t="str">
         <f t="shared" si="2"/>
@@ -16031,7 +16356,7 @@
       </c>
       <c r="R6" s="96">
         <f>SUMIFS(Cost_Components!$S$2:$S$8,Cost_Components!$G$2:$G$8,P6,Cost_Components!$D$2:$D$8,1)</f>
-        <v>4.0000000000000001E-3</v>
+        <v>0.04</v>
       </c>
       <c r="S6" s="64" t="str">
         <f t="shared" si="2"/>
@@ -16101,7 +16426,7 @@
       </c>
       <c r="R7" s="95">
         <f>SUMIFS(Cost_Components!$S$2:$S$8,Cost_Components!$G$2:$G$8,P7,Cost_Components!$D$2:$D$8,1)</f>
-        <v>4.0000000000000001E-3</v>
+        <v>0.04</v>
       </c>
       <c r="S7" s="62" t="str">
         <f t="shared" si="2"/>
@@ -16171,7 +16496,7 @@
       </c>
       <c r="R8" s="96">
         <f>SUMIFS(Cost_Components!$S$2:$S$8,Cost_Components!$G$2:$G$8,P8,Cost_Components!$D$2:$D$8,1)</f>
-        <v>4.0000000000000001E-3</v>
+        <v>0.04</v>
       </c>
       <c r="S8" s="64" t="str">
         <f t="shared" si="2"/>
@@ -16241,7 +16566,7 @@
       </c>
       <c r="R9" s="95">
         <f>SUMIFS(Cost_Components!$S$2:$S$8,Cost_Components!$G$2:$G$8,P9,Cost_Components!$D$2:$D$8,1)</f>
-        <v>4.0000000000000001E-3</v>
+        <v>0.04</v>
       </c>
       <c r="S9" s="62" t="str">
         <f t="shared" si="2"/>
@@ -16311,7 +16636,7 @@
       </c>
       <c r="R10" s="96">
         <f>SUMIFS(Cost_Components!$S$2:$S$8,Cost_Components!$G$2:$G$8,P10,Cost_Components!$D$2:$D$8,1)</f>
-        <v>4.0000000000000001E-3</v>
+        <v>0.04</v>
       </c>
       <c r="S10" s="64" t="str">
         <f t="shared" si="2"/>
@@ -17361,7 +17686,7 @@
       </c>
       <c r="R25" s="97">
         <f>SUMIFS(Cost_Components!$S$2:$S$8,Cost_Components!$G$2:$G$8,P25,Cost_Components!$D$2:$D$8,1)</f>
-        <v>4.0000000000000001E-3</v>
+        <v>0.04</v>
       </c>
       <c r="S25" s="65" t="str">
         <f t="shared" si="2"/>
@@ -17431,7 +17756,7 @@
       </c>
       <c r="R26" s="98">
         <f>SUMIFS(Cost_Components!$S$2:$S$8,Cost_Components!$G$2:$G$8,P26,Cost_Components!$D$2:$D$8,1)</f>
-        <v>4.0000000000000001E-3</v>
+        <v>0.04</v>
       </c>
       <c r="S26" s="66" t="str">
         <f t="shared" si="2"/>
@@ -17501,7 +17826,7 @@
       </c>
       <c r="R27" s="97">
         <f>SUMIFS(Cost_Components!$S$2:$S$8,Cost_Components!$G$2:$G$8,P27,Cost_Components!$D$2:$D$8,1)</f>
-        <v>4.0000000000000001E-3</v>
+        <v>0.04</v>
       </c>
       <c r="S27" s="65" t="str">
         <f t="shared" si="2"/>
@@ -17571,7 +17896,7 @@
       </c>
       <c r="R28" s="98">
         <f>SUMIFS(Cost_Components!$S$2:$S$8,Cost_Components!$G$2:$G$8,P28,Cost_Components!$D$2:$D$8,1)</f>
-        <v>4.0000000000000001E-3</v>
+        <v>0.04</v>
       </c>
       <c r="S28" s="66" t="str">
         <f t="shared" si="2"/>
@@ -17641,7 +17966,7 @@
       </c>
       <c r="R29" s="97">
         <f>SUMIFS(Cost_Components!$S$2:$S$8,Cost_Components!$G$2:$G$8,P29,Cost_Components!$D$2:$D$8,1)</f>
-        <v>4.0000000000000001E-3</v>
+        <v>0.04</v>
       </c>
       <c r="S29" s="65" t="str">
         <f t="shared" si="2"/>
